--- a/artfynd/A 58565-2025 artfynd.xlsx
+++ b/artfynd/A 58565-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61570067</v>
+        <v>61570102</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751996.313643995</v>
+        <v>752198</v>
       </c>
       <c r="R2" t="n">
-        <v>7366298.75528791</v>
+        <v>7366192</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +753,9 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,63 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61570069</v>
+        <v>114045586</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751996.313643995</v>
+        <v>752248</v>
       </c>
       <c r="R3" t="n">
-        <v>7366298.75528791</v>
+        <v>7366171</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,38 +866,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61570064</v>
+        <v>114045616</v>
       </c>
       <c r="B4" t="n">
-        <v>90130</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,47 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1958</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751996.313643995</v>
+        <v>752149</v>
       </c>
       <c r="R4" t="n">
-        <v>7366298.75528791</v>
+        <v>7366180</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,38 +963,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61570102</v>
+        <v>114483406</v>
       </c>
       <c r="B5" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,30 +1009,20 @@
           <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Kilkok 6, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752197.7875308007</v>
+        <v>751965</v>
       </c>
       <c r="R5" t="n">
-        <v>7366191.637405674</v>
+        <v>7366262</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,64 +1060,72 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>med Överståndare</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61570068</v>
+        <v>61570064</v>
       </c>
       <c r="B6" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751996.313643995</v>
+        <v>751996</v>
       </c>
       <c r="R6" t="n">
-        <v>7366298.75528791</v>
+        <v>7366299</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,19 +1166,9 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,53 +1200,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114045584</v>
+        <v>61570067</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752179</v>
+        <v>751996</v>
       </c>
       <c r="R7" t="n">
-        <v>7366195</v>
+        <v>7366299</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,33 +1281,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114045586</v>
+        <v>61570078</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,37 +1315,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752248</v>
+        <v>752046</v>
       </c>
       <c r="R8" t="n">
-        <v>7366171</v>
+        <v>7366313</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,12 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,33 +1385,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114045652</v>
+        <v>61570069</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,20 +1436,30 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751974</v>
+        <v>751996</v>
       </c>
       <c r="R9" t="n">
-        <v>7366291</v>
+        <v>7366299</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,12 +1483,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,33 +1497,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114045642</v>
+        <v>114045600</v>
       </c>
       <c r="B10" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752232</v>
+        <v>752153</v>
       </c>
       <c r="R10" t="n">
-        <v>7366131</v>
+        <v>7366213</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,37 +1617,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114045604</v>
+        <v>114045611</v>
       </c>
       <c r="B11" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752141</v>
+        <v>752212</v>
       </c>
       <c r="R11" t="n">
-        <v>7366233</v>
+        <v>7366186</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,37 +1714,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114045594</v>
+        <v>114045642</v>
       </c>
       <c r="B12" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752166</v>
+        <v>752232</v>
       </c>
       <c r="R12" t="n">
-        <v>7366208</v>
+        <v>7366131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,15 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114045669</v>
+        <v>114045652</v>
       </c>
       <c r="B13" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752138</v>
+        <v>751974</v>
       </c>
       <c r="R13" t="n">
-        <v>7366204</v>
+        <v>7366291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,15 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114045600</v>
+        <v>114045669</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752153</v>
+        <v>752138</v>
       </c>
       <c r="R14" t="n">
-        <v>7366213</v>
+        <v>7366204</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,15 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114045611</v>
+        <v>61570068</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,37 +2016,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752212</v>
+        <v>751996</v>
       </c>
       <c r="R15" t="n">
-        <v>7366186</v>
+        <v>7366299</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,12 +2072,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,71 +2086,73 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114045663</v>
+        <v>61570077</v>
       </c>
       <c r="B16" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752188</v>
+        <v>752046</v>
       </c>
       <c r="R16" t="n">
-        <v>7366179</v>
+        <v>7366313</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2282,12 +2176,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,33 +2190,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114045630</v>
+        <v>114045584</v>
       </c>
       <c r="B17" t="n">
-        <v>91648</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2224,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2354,10 +2248,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752238</v>
+        <v>752179</v>
       </c>
       <c r="R17" t="n">
-        <v>7366109</v>
+        <v>7366195</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2416,37 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114045667</v>
+        <v>114045634</v>
       </c>
       <c r="B18" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752162</v>
+        <v>752076</v>
       </c>
       <c r="R18" t="n">
-        <v>7366207</v>
+        <v>7366220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,12 +2410,7 @@
         <v>114045650</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,37 +2504,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114045616</v>
+        <v>114045617</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>149</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2660,10 +2539,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752149</v>
+        <v>752289</v>
       </c>
       <c r="R20" t="n">
-        <v>7366180</v>
+        <v>7366061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,15 +2601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114406647</v>
+        <v>114045585</v>
       </c>
       <c r="B21" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,37 +2612,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kilkok 3, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751974</v>
+        <v>751949</v>
       </c>
       <c r="R21" t="n">
-        <v>7366258</v>
+        <v>7366299</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,12 +2666,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,44 +2680,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>äldre,ca 90 år</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114483406</v>
+        <v>114045594</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,34 +2709,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>149</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kilkok 6, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751965</v>
+        <v>752166</v>
       </c>
       <c r="R22" t="n">
-        <v>7366262</v>
+        <v>7366208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,12 +2763,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,29 +2779,615 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>med Överståndare</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114045667</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>752162</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7366207</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114045597</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>752310</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7366081</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114045604</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>752141</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7366233</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114045663</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>752188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7366179</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114045630</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>752238</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7366109</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114406647</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kilkok 3, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>751974</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7366258</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>äldre,ca 90 år</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58565-2025 artfynd.xlsx
+++ b/artfynd/A 58565-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570102</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045616</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114483406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570064</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570067</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570078</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570069</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045600</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045611</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045642</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045652</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045669</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570068</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61570077</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045584</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045634</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2501,6 +2591,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045650</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2598,6 +2693,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045617</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2695,6 +2795,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045585</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2792,6 +2897,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045594</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045667</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2986,6 +3101,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045597</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3083,6 +3203,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045604</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3180,6 +3305,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045663</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3277,6 +3407,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114045630</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3388,8 +3523,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114406647</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>